--- a/jogos_2025-06-29.xlsx
+++ b/jogos_2025-06-29.xlsx
@@ -277,12 +277,12 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
@@ -298,18 +298,18 @@
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>Belarus Vysheyshaya Liga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -337,18 +337,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Marconi Stallions</t>
+  </si>
+  <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
-    <t>Marconi Stallions</t>
-  </si>
-  <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
@@ -358,30 +358,30 @@
     <t>Albirex Niigata</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
+    <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
-    <t>Changchun Yatai</t>
+    <t>Örebro</t>
   </si>
   <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
@@ -403,54 +403,54 @@
     <t>Tobol</t>
   </si>
   <si>
+    <t>Turan Turkistan</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Turan Turkistan</t>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Bunyodkor</t>
+  </si>
+  <si>
+    <t>Naftan</t>
   </si>
   <si>
     <t>Víkingur</t>
   </si>
   <si>
-    <t>Bunyodkor</t>
-  </si>
-  <si>
-    <t>Naftan</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
+    <t>Häcken</t>
   </si>
   <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Häcken</t>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Kaisar</t>
   </si>
   <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Astana</t>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Bryne</t>
   </si>
   <si>
     <t>Buxoro</t>
   </si>
   <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
@@ -484,27 +484,27 @@
     <t>Alvarado</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
     <t>Estudiantes Río Cuarto</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>Athletic Club</t>
+    <t>Víkingur Reykjavík</t>
   </si>
   <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Víkingur Reykjavík</t>
-  </si>
-  <si>
     <t>ABC</t>
   </si>
   <si>
@@ -547,18 +547,18 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
+    <t>NWS Spirit</t>
+  </si>
+  <si>
+    <t>Sutherland Sharks</t>
+  </si>
+  <si>
     <t>Mt Druitt Town</t>
   </si>
   <si>
-    <t>NWS Spirit</t>
-  </si>
-  <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
-    <t>Sutherland Sharks</t>
-  </si>
-  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
@@ -568,30 +568,30 @@
     <t>Machida Zelvia</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
+    <t>Shanghai Shenhua</t>
   </si>
   <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
+    <t>Kalmar</t>
   </si>
   <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
     <t>Dongguan United</t>
   </si>
   <si>
@@ -613,54 +613,54 @@
     <t>Zhenys</t>
   </si>
   <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
     <t>Umeå</t>
   </si>
   <si>
-    <t>Aktobe</t>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>BATE</t>
   </si>
   <si>
     <t>B68</t>
   </si>
   <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
-    <t>BATE</t>
-  </si>
-  <si>
-    <t>Kuressaare</t>
+    <t>GAIS</t>
   </si>
   <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>GAIS</t>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
   </si>
   <si>
     <t>Åsane</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>HamKam</t>
   </si>
   <si>
     <t>Shortan</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
@@ -694,25 +694,25 @@
     <t>Racing Córdoba</t>
   </si>
   <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>Operário PR</t>
   </si>
   <si>
+    <t>Almagro</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Almagro</t>
-  </si>
-  <si>
     <t>Huntsville City</t>
   </si>
   <si>
-    <t>Remo</t>
+    <t>Afturelding</t>
   </si>
   <si>
     <t>FH</t>
-  </si>
-  <si>
-    <t>Afturelding</t>
   </si>
   <si>
     <t>Ypiranga Erechim</t>
@@ -1332,76 +1332,76 @@
         <v>247</v>
       </c>
       <c r="L2">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
-        <v>3.6</v>
+        <v>4.48</v>
       </c>
       <c r="N2">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB2">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AC2">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>248</v>
@@ -1410,13 +1410,13 @@
         <v>248</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW2">
         <v>0</v>
@@ -1458,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BD2" s="3">
         <v>45837.08333333334</v>
@@ -1672,76 +1672,76 @@
         <v>247</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="M4">
-        <v>4.48</v>
+        <v>8.34</v>
       </c>
       <c r="N4">
+        <v>9.4</v>
+      </c>
+      <c r="O4">
+        <v>1.17</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4">
         <v>5</v>
       </c>
-      <c r="O4">
-        <v>1.36</v>
-      </c>
-      <c r="P4">
-        <v>14.25</v>
-      </c>
-      <c r="Q4">
-        <v>3.25</v>
-      </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="W4">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>14.2</v>
+        <v>34</v>
       </c>
       <c r="Z4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AA4">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="AB4">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AC4">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="AE4">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="AF4">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH4">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="AI4">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AJ4" t="s">
         <v>248</v>
@@ -1750,13 +1750,13 @@
         <v>248</v>
       </c>
       <c r="AL4">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AM4">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AN4">
-        <v>2.42</v>
+        <v>4.75</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AV4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW4">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="BC4">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="BD4" s="3">
         <v>45837.08333333334</v>
@@ -1842,76 +1842,76 @@
         <v>247</v>
       </c>
       <c r="L5">
-        <v>1.12</v>
+        <v>2.45</v>
       </c>
       <c r="M5">
-        <v>8.34</v>
+        <v>3.6</v>
       </c>
       <c r="N5">
-        <v>9.4</v>
+        <v>2.35</v>
       </c>
       <c r="O5">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC5">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD5">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
         <v>248</v>
@@ -1920,13 +1920,13 @@
         <v>248</v>
       </c>
       <c r="AL5">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BD5" s="3">
         <v>45837.08333333334</v>
@@ -2522,73 +2522,73 @@
         <v>247</v>
       </c>
       <c r="L9">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="M9">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="N9">
-        <v>3.31</v>
+        <v>3.58</v>
       </c>
       <c r="O9">
         <v>1.62</v>
       </c>
       <c r="P9">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="Q9">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
+        <v>1.5</v>
+      </c>
+      <c r="S9">
+        <v>2.5</v>
+      </c>
+      <c r="T9">
+        <v>3.4</v>
+      </c>
+      <c r="U9">
         <v>1.3</v>
       </c>
-      <c r="S9">
-        <v>3.2</v>
-      </c>
-      <c r="T9">
-        <v>2.5</v>
-      </c>
-      <c r="U9">
-        <v>1.44</v>
-      </c>
       <c r="V9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Z9">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AA9">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="AC9">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AD9">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AE9">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH9">
-        <v>6.05</v>
+        <v>8.5</v>
       </c>
       <c r="AI9">
         <v>1.06</v>
@@ -2600,46 +2600,46 @@
         <v>248</v>
       </c>
       <c r="AL9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AM9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AQ9">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AR9">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AS9">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AT9">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AU9">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="AV9">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AW9">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AX9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AY9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>1.62</v>
       </c>
       <c r="BC9">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="BD9" s="3">
         <v>45837.29166666666</v>
@@ -2692,76 +2692,76 @@
         <v>247</v>
       </c>
       <c r="L10">
-        <v>1.94</v>
+        <v>3.69</v>
       </c>
       <c r="M10">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N10">
-        <v>3.58</v>
+        <v>1.86</v>
       </c>
       <c r="O10">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="P10">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q10">
+        <v>1.67</v>
+      </c>
+      <c r="R10">
+        <v>1.4</v>
+      </c>
+      <c r="S10">
         <v>2.75</v>
       </c>
-      <c r="R10">
-        <v>1.5</v>
-      </c>
-      <c r="S10">
-        <v>2.5</v>
-      </c>
       <c r="T10">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AA10">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AB10">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD10">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AE10">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG10">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH10">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="s">
         <v>248</v>
@@ -2770,46 +2770,46 @@
         <v>248</v>
       </c>
       <c r="AL10">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AM10">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AN10">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AQ10">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AR10">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AS10">
-        <v>2.8</v>
+        <v>3.86</v>
       </c>
       <c r="AT10">
-        <v>3.8</v>
+        <v>4.95</v>
       </c>
       <c r="AU10">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="AV10">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AW10">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AX10">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AY10">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2818,10 +2818,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="BC10">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="BD10" s="3">
         <v>45837.29166666666</v>
@@ -2835,7 +2835,7 @@
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
         <v>106</v>
@@ -2862,40 +2862,40 @@
         <v>247</v>
       </c>
       <c r="L11">
-        <v>3.69</v>
+        <v>2.88</v>
       </c>
       <c r="M11">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="N11">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="O11">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="P11">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R11">
+        <v>1.36</v>
+      </c>
+      <c r="S11">
+        <v>2.9</v>
+      </c>
+      <c r="T11">
+        <v>2.8</v>
+      </c>
+      <c r="U11">
         <v>1.4</v>
       </c>
-      <c r="S11">
-        <v>2.75</v>
-      </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
-      <c r="U11">
-        <v>1.36</v>
-      </c>
       <c r="V11">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2904,82 +2904,82 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z11">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AA11">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
+        <v>1.83</v>
+      </c>
+      <c r="AD11">
+        <v>3.2</v>
+      </c>
+      <c r="AE11">
+        <v>1.26</v>
+      </c>
+      <c r="AF11">
+        <v>1.73</v>
+      </c>
+      <c r="AG11">
+        <v>2.05</v>
+      </c>
+      <c r="AH11">
+        <v>6.45</v>
+      </c>
+      <c r="AI11">
+        <v>1.05</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL11">
         <v>1.65</v>
       </c>
-      <c r="AD11">
-        <v>4.15</v>
-      </c>
-      <c r="AE11">
-        <v>1.16</v>
-      </c>
-      <c r="AF11">
-        <v>1.91</v>
-      </c>
-      <c r="AG11">
-        <v>1.83</v>
-      </c>
-      <c r="AH11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AI11">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL11">
-        <v>1.85</v>
-      </c>
       <c r="AM11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN11">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AQ11">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AR11">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AS11">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AT11">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AU11">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AV11">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AW11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AX11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AY11">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2988,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="BC11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BD11" s="3">
         <v>45837.29166666666</v>
@@ -3005,7 +3005,7 @@
         <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
         <v>106</v>
@@ -3032,76 +3032,76 @@
         <v>247</v>
       </c>
       <c r="L12">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="M12">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="N12">
-        <v>2.08</v>
+        <v>3.31</v>
       </c>
       <c r="O12">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="P12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AA12">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC12">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AD12">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE12">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH12">
-        <v>6.45</v>
+        <v>6.05</v>
       </c>
       <c r="AI12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
         <v>248</v>
@@ -3110,46 +3110,46 @@
         <v>248</v>
       </c>
       <c r="AL12">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="AM12">
         <v>1.3</v>
       </c>
       <c r="AN12">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AQ12">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AR12">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="AS12">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="AT12">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AU12">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="AV12">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AW12">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AX12">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AY12">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -3158,10 +3158,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="BC12">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="BD12" s="3">
         <v>45837.29166666666</v>
@@ -3202,76 +3202,76 @@
         <v>247</v>
       </c>
       <c r="L13">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="M13">
-        <v>4.33</v>
+        <v>5.3</v>
       </c>
       <c r="N13">
-        <v>6.25</v>
+        <v>1.29</v>
       </c>
       <c r="O13">
-        <v>1.4</v>
+        <v>3.74</v>
       </c>
       <c r="P13">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Q13">
-        <v>3.12</v>
+        <v>1.28</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S13">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="T13">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U13">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="V13">
-        <v>5.75</v>
+        <v>5.1</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z13">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AA13">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="AB13">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AC13">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="AD13">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AE13">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH13">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="AI13">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ13" t="s">
         <v>248</v>
@@ -3280,46 +3280,46 @@
         <v>248</v>
       </c>
       <c r="AL13">
-        <v>1.11</v>
+        <v>3.28</v>
       </c>
       <c r="AM13">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AN13">
-        <v>2.52</v>
+        <v>1.06</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR13">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS13">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AT13">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AU13">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AV13">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AW13">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AX13">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AY13">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.4</v>
+        <v>3.74</v>
       </c>
       <c r="BC13">
-        <v>3.12</v>
+        <v>1.28</v>
       </c>
       <c r="BD13" s="3">
         <v>45837.3125</v>
@@ -3372,76 +3372,76 @@
         <v>247</v>
       </c>
       <c r="L14">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="M14">
-        <v>5.3</v>
+        <v>4.33</v>
       </c>
       <c r="N14">
-        <v>1.29</v>
+        <v>6.25</v>
       </c>
       <c r="O14">
-        <v>3.74</v>
+        <v>1.4</v>
       </c>
       <c r="P14">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Q14">
-        <v>1.28</v>
+        <v>3.12</v>
       </c>
       <c r="R14">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S14">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="T14">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U14">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="V14">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z14">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AA14">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="AB14">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AC14">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="AD14">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AE14">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH14">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="AI14">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="s">
         <v>248</v>
@@ -3450,46 +3450,46 @@
         <v>248</v>
       </c>
       <c r="AL14">
-        <v>3.28</v>
+        <v>1.11</v>
       </c>
       <c r="AM14">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AN14">
-        <v>1.06</v>
+        <v>2.52</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AS14">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AT14">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AU14">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="AV14">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AW14">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AX14">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AY14">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3498,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>3.74</v>
+        <v>1.4</v>
       </c>
       <c r="BC14">
-        <v>1.28</v>
+        <v>3.12</v>
       </c>
       <c r="BD14" s="3">
         <v>45837.3125</v>
@@ -3515,7 +3515,7 @@
         <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>106</v>
@@ -3542,76 +3542,76 @@
         <v>247</v>
       </c>
       <c r="L15">
-        <v>2.59</v>
+        <v>3.95</v>
       </c>
       <c r="M15">
-        <v>3.68</v>
+        <v>3.53</v>
       </c>
       <c r="N15">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="O15">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="P15">
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="R15">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T15">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="U15">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V15">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA15">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB15">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AD15">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AE15">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH15">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="AI15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ15" t="s">
         <v>248</v>
@@ -3620,46 +3620,46 @@
         <v>248</v>
       </c>
       <c r="AL15">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AM15">
         <v>1.22</v>
       </c>
       <c r="AN15">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AQ15">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AR15">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AS15">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AT15">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AU15">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AV15">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AW15">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AX15">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AY15">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3668,10 +3668,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="BC15">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="BD15" s="3">
         <v>45837.33333333334</v>
@@ -3685,7 +3685,7 @@
         <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>106</v>
@@ -3712,76 +3712,76 @@
         <v>247</v>
       </c>
       <c r="L16">
-        <v>3.95</v>
+        <v>2.59</v>
       </c>
       <c r="M16">
-        <v>3.53</v>
+        <v>3.68</v>
       </c>
       <c r="N16">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="O16">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="P16">
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="R16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T16">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="U16">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V16">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA16">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AC16">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AD16">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AE16">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH16">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AI16">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ16" t="s">
         <v>248</v>
@@ -3790,46 +3790,46 @@
         <v>248</v>
       </c>
       <c r="AL16">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AM16">
         <v>1.22</v>
       </c>
       <c r="AN16">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AQ16">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AR16">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AS16">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AT16">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AU16">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AV16">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AW16">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AX16">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AY16">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="BC16">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="BD16" s="3">
         <v>45837.33333333334</v>
@@ -5045,7 +5045,7 @@
         <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>106</v>
@@ -5072,124 +5072,124 @@
         <v>247</v>
       </c>
       <c r="L24">
-        <v>1.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M24">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N24">
-        <v>6.5</v>
+        <v>1.31</v>
       </c>
       <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>1.49</v>
+      </c>
+      <c r="S24">
+        <v>2.8</v>
+      </c>
+      <c r="T24">
+        <v>2.8</v>
+      </c>
+      <c r="U24">
         <v>1.33</v>
       </c>
-      <c r="P24">
-        <v>17.25</v>
-      </c>
-      <c r="Q24">
-        <v>3.4</v>
-      </c>
-      <c r="R24">
-        <v>1.25</v>
-      </c>
-      <c r="S24">
-        <v>3.42</v>
-      </c>
-      <c r="T24">
-        <v>2.36</v>
-      </c>
-      <c r="U24">
-        <v>1.55</v>
-      </c>
       <c r="V24">
-        <v>5.15</v>
+        <v>7</v>
       </c>
       <c r="W24">
+        <v>1.07</v>
+      </c>
+      <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>8.5</v>
+      </c>
+      <c r="Z24">
+        <v>1.3</v>
+      </c>
+      <c r="AA24">
+        <v>2.97</v>
+      </c>
+      <c r="AB24">
+        <v>2.23</v>
+      </c>
+      <c r="AC24">
+        <v>1.62</v>
+      </c>
+      <c r="AD24">
+        <v>3.2</v>
+      </c>
+      <c r="AE24">
+        <v>1.24</v>
+      </c>
+      <c r="AF24">
+        <v>2.55</v>
+      </c>
+      <c r="AG24">
+        <v>1.42</v>
+      </c>
+      <c r="AH24">
+        <v>6.2</v>
+      </c>
+      <c r="AI24">
+        <v>1.08</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL24">
         <v>1.11</v>
       </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>12</v>
-      </c>
-      <c r="Z24">
-        <v>1.15</v>
-      </c>
-      <c r="AA24">
-        <v>4.3</v>
-      </c>
-      <c r="AB24">
-        <v>1.57</v>
-      </c>
-      <c r="AC24">
-        <v>2.15</v>
-      </c>
-      <c r="AD24">
-        <v>2.39</v>
-      </c>
-      <c r="AE24">
-        <v>1.46</v>
-      </c>
-      <c r="AF24">
-        <v>1.83</v>
-      </c>
-      <c r="AG24">
-        <v>1.87</v>
-      </c>
-      <c r="AH24">
-        <v>4.15</v>
-      </c>
-      <c r="AI24">
-        <v>1.16</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL24">
-        <v>1.1</v>
-      </c>
       <c r="AM24">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ24">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR24">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS24">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT24">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU24">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AV24">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW24">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX24">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY24">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -5198,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC24">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BD24" s="3">
         <v>45837.41666666666</v>
@@ -5215,7 +5215,7 @@
         <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
         <v>106</v>
@@ -5242,124 +5242,124 @@
         <v>247</v>
       </c>
       <c r="L25">
-        <v>8.800000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="M25">
+        <v>4.5</v>
+      </c>
+      <c r="N25">
+        <v>6.5</v>
+      </c>
+      <c r="O25">
+        <v>1.33</v>
+      </c>
+      <c r="P25">
+        <v>17.25</v>
+      </c>
+      <c r="Q25">
+        <v>3.4</v>
+      </c>
+      <c r="R25">
+        <v>1.25</v>
+      </c>
+      <c r="S25">
+        <v>3.42</v>
+      </c>
+      <c r="T25">
+        <v>2.36</v>
+      </c>
+      <c r="U25">
+        <v>1.55</v>
+      </c>
+      <c r="V25">
+        <v>5.15</v>
+      </c>
+      <c r="W25">
+        <v>1.11</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>12</v>
+      </c>
+      <c r="Z25">
+        <v>1.15</v>
+      </c>
+      <c r="AA25">
         <v>4.3</v>
       </c>
-      <c r="N25">
-        <v>1.31</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>1.49</v>
-      </c>
-      <c r="S25">
+      <c r="AB25">
+        <v>1.57</v>
+      </c>
+      <c r="AC25">
+        <v>2.15</v>
+      </c>
+      <c r="AD25">
+        <v>2.39</v>
+      </c>
+      <c r="AE25">
+        <v>1.46</v>
+      </c>
+      <c r="AF25">
+        <v>1.83</v>
+      </c>
+      <c r="AG25">
+        <v>1.87</v>
+      </c>
+      <c r="AH25">
+        <v>4.15</v>
+      </c>
+      <c r="AI25">
+        <v>1.16</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL25">
+        <v>1.1</v>
+      </c>
+      <c r="AM25">
+        <v>1.14</v>
+      </c>
+      <c r="AN25">
         <v>2.8</v>
-      </c>
-      <c r="T25">
-        <v>2.8</v>
-      </c>
-      <c r="U25">
-        <v>1.33</v>
-      </c>
-      <c r="V25">
-        <v>7</v>
-      </c>
-      <c r="W25">
-        <v>1.07</v>
-      </c>
-      <c r="X25">
-        <v>1.04</v>
-      </c>
-      <c r="Y25">
-        <v>8.5</v>
-      </c>
-      <c r="Z25">
-        <v>1.3</v>
-      </c>
-      <c r="AA25">
-        <v>2.97</v>
-      </c>
-      <c r="AB25">
-        <v>2.23</v>
-      </c>
-      <c r="AC25">
-        <v>1.62</v>
-      </c>
-      <c r="AD25">
-        <v>3.2</v>
-      </c>
-      <c r="AE25">
-        <v>1.24</v>
-      </c>
-      <c r="AF25">
-        <v>2.55</v>
-      </c>
-      <c r="AG25">
-        <v>1.42</v>
-      </c>
-      <c r="AH25">
-        <v>6.2</v>
-      </c>
-      <c r="AI25">
-        <v>1.08</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL25">
-        <v>1.11</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>1.03</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5368,10 +5368,10 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BD25" s="3">
         <v>45837.41666666666</v>
@@ -5412,76 +5412,76 @@
         <v>247</v>
       </c>
       <c r="L26">
-        <v>1.26</v>
+        <v>1.94</v>
       </c>
       <c r="M26">
-        <v>5.5</v>
+        <v>3.57</v>
       </c>
       <c r="N26">
-        <v>8</v>
+        <v>3.08</v>
       </c>
       <c r="O26">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="P26">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Q26">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="R26">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S26">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T26">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="U26">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="V26">
-        <v>3.9</v>
+        <v>5.15</v>
       </c>
       <c r="W26">
+        <v>1.14</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>13</v>
+      </c>
+      <c r="Z26">
         <v>1.2</v>
       </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>15</v>
-      </c>
-      <c r="Z26">
-        <v>1.13</v>
-      </c>
       <c r="AA26">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB26">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AD26">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AE26">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AG26">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="AH26">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AI26">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="s">
         <v>248</v>
@@ -5490,13 +5490,13 @@
         <v>248</v>
       </c>
       <c r="AL26">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AM26">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AN26">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO26">
         <v>-1</v>
@@ -5538,10 +5538,10 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="BC26">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="BD26" s="3">
         <v>45837.45833333334</v>
@@ -5922,76 +5922,76 @@
         <v>247</v>
       </c>
       <c r="L29">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="M29">
-        <v>3.57</v>
+        <v>5.5</v>
       </c>
       <c r="N29">
-        <v>3.08</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="P29">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="Q29">
-        <v>2.38</v>
+        <v>3.48</v>
       </c>
       <c r="R29">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S29">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="T29">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="U29">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="V29">
-        <v>5.15</v>
+        <v>3.9</v>
       </c>
       <c r="W29">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z29">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AA29">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AC29">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AD29">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AE29">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AF29">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="AH29">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AI29">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AJ29" t="s">
         <v>248</v>
@@ -6000,13 +6000,13 @@
         <v>248</v>
       </c>
       <c r="AL29">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AM29">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AN29">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO29">
         <v>-1</v>
@@ -6048,10 +6048,10 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="BC29">
-        <v>2.38</v>
+        <v>3.48</v>
       </c>
       <c r="BD29" s="3">
         <v>45837.45833333334</v>
@@ -6092,76 +6092,76 @@
         <v>247</v>
       </c>
       <c r="L30">
-        <v>3.45</v>
+        <v>2.33</v>
       </c>
       <c r="M30">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="N30">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O30">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="P30">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="R30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T30">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA30">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AB30">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AC30">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD30">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="AE30">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH30">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="AI30">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AJ30" t="s">
         <v>248</v>
@@ -6170,46 +6170,46 @@
         <v>248</v>
       </c>
       <c r="AL30">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AM30">
         <v>1.25</v>
       </c>
       <c r="AN30">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AQ30">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AR30">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AS30">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AT30">
+        <v>1.88</v>
+      </c>
+      <c r="AU30">
+        <v>5.4</v>
+      </c>
+      <c r="AV30">
+        <v>3.9</v>
+      </c>
+      <c r="AW30">
+        <v>2.88</v>
+      </c>
+      <c r="AX30">
         <v>2.23</v>
       </c>
-      <c r="AU30">
-        <v>4.2</v>
-      </c>
-      <c r="AV30">
-        <v>3.05</v>
-      </c>
-      <c r="AW30">
-        <v>2.33</v>
-      </c>
-      <c r="AX30">
-        <v>1.88</v>
-      </c>
       <c r="AY30">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AZ30">
         <v>0</v>
@@ -6218,10 +6218,10 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="BC30">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="BD30" s="3">
         <v>45837.47916666666</v>
@@ -6262,76 +6262,76 @@
         <v>247</v>
       </c>
       <c r="L31">
-        <v>2.33</v>
+        <v>3.45</v>
       </c>
       <c r="M31">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="N31">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O31">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="P31">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="T31">
+        <v>2.63</v>
+      </c>
+      <c r="U31">
+        <v>1.44</v>
+      </c>
+      <c r="V31">
+        <v>7</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.06</v>
+      </c>
+      <c r="Y31">
+        <v>9.5</v>
+      </c>
+      <c r="Z31">
+        <v>1.3</v>
+      </c>
+      <c r="AA31">
+        <v>3.55</v>
+      </c>
+      <c r="AB31">
+        <v>1.82</v>
+      </c>
+      <c r="AC31">
+        <v>1.88</v>
+      </c>
+      <c r="AD31">
         <v>3.25</v>
       </c>
-      <c r="T31">
-        <v>2.5</v>
-      </c>
-      <c r="U31">
-        <v>1.5</v>
-      </c>
-      <c r="V31">
-        <v>6.5</v>
-      </c>
-      <c r="W31">
-        <v>1.11</v>
-      </c>
-      <c r="X31">
-        <v>1.05</v>
-      </c>
-      <c r="Y31">
-        <v>10</v>
-      </c>
-      <c r="Z31">
-        <v>1.25</v>
-      </c>
-      <c r="AA31">
-        <v>4</v>
-      </c>
-      <c r="AB31">
-        <v>1.62</v>
-      </c>
-      <c r="AC31">
-        <v>2.15</v>
-      </c>
-      <c r="AD31">
-        <v>2.85</v>
-      </c>
       <c r="AE31">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH31">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI31">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="s">
         <v>248</v>
@@ -6340,58 +6340,58 @@
         <v>248</v>
       </c>
       <c r="AL31">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AM31">
         <v>1.25</v>
       </c>
       <c r="AN31">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ31">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AR31">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AS31">
+        <v>1.81</v>
+      </c>
+      <c r="AT31">
+        <v>2.23</v>
+      </c>
+      <c r="AU31">
+        <v>4.2</v>
+      </c>
+      <c r="AV31">
+        <v>3.05</v>
+      </c>
+      <c r="AW31">
+        <v>2.33</v>
+      </c>
+      <c r="AX31">
+        <v>1.88</v>
+      </c>
+      <c r="AY31">
+        <v>1.56</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>2.6</v>
+      </c>
+      <c r="BC31">
         <v>1.57</v>
-      </c>
-      <c r="AT31">
-        <v>1.88</v>
-      </c>
-      <c r="AU31">
-        <v>5.4</v>
-      </c>
-      <c r="AV31">
-        <v>3.9</v>
-      </c>
-      <c r="AW31">
-        <v>2.88</v>
-      </c>
-      <c r="AX31">
-        <v>2.23</v>
-      </c>
-      <c r="AY31">
-        <v>1.82</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.83</v>
-      </c>
-      <c r="BC31">
-        <v>2.05</v>
       </c>
       <c r="BD31" s="3">
         <v>45837.47916666666</v>
@@ -6405,7 +6405,7 @@
         <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>106</v>
@@ -6432,124 +6432,124 @@
         <v>247</v>
       </c>
       <c r="L32">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="M32">
-        <v>3.92</v>
+        <v>3.08</v>
       </c>
       <c r="N32">
         <v>2.85</v>
       </c>
       <c r="O32">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="P32">
-        <v>16.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q32">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R32">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="S32">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="T32">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
+        <v>1.3</v>
+      </c>
+      <c r="V32">
+        <v>9.1</v>
+      </c>
+      <c r="W32">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>1.08</v>
+      </c>
+      <c r="Y32">
+        <v>7.5</v>
+      </c>
+      <c r="Z32">
+        <v>1.42</v>
+      </c>
+      <c r="AA32">
+        <v>2.8</v>
+      </c>
+      <c r="AB32">
+        <v>2.04</v>
+      </c>
+      <c r="AC32">
+        <v>1.69</v>
+      </c>
+      <c r="AD32">
+        <v>4.2</v>
+      </c>
+      <c r="AE32">
+        <v>1.22</v>
+      </c>
+      <c r="AF32">
+        <v>1.85</v>
+      </c>
+      <c r="AG32">
+        <v>1.8</v>
+      </c>
+      <c r="AH32">
+        <v>8.5</v>
+      </c>
+      <c r="AI32">
+        <v>1.06</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL32">
+        <v>1.38</v>
+      </c>
+      <c r="AM32">
+        <v>1.3</v>
+      </c>
+      <c r="AN32">
         <v>1.53</v>
-      </c>
-      <c r="V32">
-        <v>4.5</v>
-      </c>
-      <c r="W32">
-        <v>1.14</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>12</v>
-      </c>
-      <c r="Z32">
-        <v>1.14</v>
-      </c>
-      <c r="AA32">
-        <v>4.5</v>
-      </c>
-      <c r="AB32">
-        <v>1.55</v>
-      </c>
-      <c r="AC32">
-        <v>2.2</v>
-      </c>
-      <c r="AD32">
-        <v>2.4</v>
-      </c>
-      <c r="AE32">
-        <v>1.5</v>
-      </c>
-      <c r="AF32">
-        <v>1.48</v>
-      </c>
-      <c r="AG32">
-        <v>2.3</v>
-      </c>
-      <c r="AH32">
-        <v>4</v>
-      </c>
-      <c r="AI32">
-        <v>1.2</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL32">
-        <v>1.23</v>
-      </c>
-      <c r="AM32">
-        <v>1.26</v>
-      </c>
-      <c r="AN32">
-        <v>1.7</v>
       </c>
       <c r="AO32">
         <v>-1</v>
       </c>
       <c r="AP32">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AR32">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AS32">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AT32">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="AU32">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="AV32">
-        <v>3.28</v>
+        <v>2.23</v>
       </c>
       <c r="AW32">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="AX32">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="AY32">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AZ32">
         <v>0</v>
@@ -6558,10 +6558,10 @@
         <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="BC32">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BD32" s="3">
         <v>45837.5</v>
@@ -6602,13 +6602,13 @@
         <v>247</v>
       </c>
       <c r="L33">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="M33">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N33">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -6620,58 +6620,58 @@
         <v>0</v>
       </c>
       <c r="R33">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S33">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T33">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U33">
+        <v>1.35</v>
+      </c>
+      <c r="V33">
+        <v>6.95</v>
+      </c>
+      <c r="W33">
+        <v>1.04</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
+        <v>8.1</v>
+      </c>
+      <c r="Z33">
         <v>1.3</v>
       </c>
-      <c r="V33">
-        <v>8</v>
-      </c>
-      <c r="W33">
-        <v>1.05</v>
-      </c>
-      <c r="X33">
+      <c r="AA33">
+        <v>2.97</v>
+      </c>
+      <c r="AB33">
+        <v>2.03</v>
+      </c>
+      <c r="AC33">
+        <v>1.75</v>
+      </c>
+      <c r="AD33">
+        <v>3.42</v>
+      </c>
+      <c r="AE33">
+        <v>1.27</v>
+      </c>
+      <c r="AF33">
+        <v>1.8</v>
+      </c>
+      <c r="AG33">
+        <v>1.96</v>
+      </c>
+      <c r="AH33">
+        <v>6.5</v>
+      </c>
+      <c r="AI33">
         <v>1.07</v>
-      </c>
-      <c r="Y33">
-        <v>6.8</v>
-      </c>
-      <c r="Z33">
-        <v>1.38</v>
-      </c>
-      <c r="AA33">
-        <v>2.85</v>
-      </c>
-      <c r="AB33">
-        <v>2.23</v>
-      </c>
-      <c r="AC33">
-        <v>1.62</v>
-      </c>
-      <c r="AD33">
-        <v>3.8</v>
-      </c>
-      <c r="AE33">
-        <v>1.22</v>
-      </c>
-      <c r="AF33">
-        <v>1.87</v>
-      </c>
-      <c r="AG33">
-        <v>1.77</v>
-      </c>
-      <c r="AH33">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AI33">
-        <v>1.05</v>
       </c>
       <c r="AJ33" t="s">
         <v>248</v>
@@ -6686,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="AN33">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AO33">
         <v>-1</v>
@@ -6772,13 +6772,13 @@
         <v>247</v>
       </c>
       <c r="L34">
-        <v>3.45</v>
+        <v>1.29</v>
       </c>
       <c r="M34">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N34">
-        <v>1.95</v>
+        <v>9.4</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -6793,55 +6793,55 @@
         <v>1.42</v>
       </c>
       <c r="S34">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U34">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="V34">
-        <v>6.95</v>
+        <v>7.3</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AA34">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AB34">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AD34">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="AE34">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AG34">
-        <v>1.96</v>
+        <v>1.42</v>
       </c>
       <c r="AH34">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AI34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ34" t="s">
         <v>248</v>
@@ -6850,13 +6850,13 @@
         <v>248</v>
       </c>
       <c r="AL34">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AM34">
         <v>0</v>
       </c>
       <c r="AN34">
-        <v>1.22</v>
+        <v>3.7</v>
       </c>
       <c r="AO34">
         <v>-1</v>
@@ -6942,13 +6942,13 @@
         <v>247</v>
       </c>
       <c r="L35">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="M35">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="N35">
-        <v>9.4</v>
+        <v>2.14</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -6960,58 +6960,58 @@
         <v>0</v>
       </c>
       <c r="R35">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S35">
+        <v>2.5</v>
+      </c>
+      <c r="T35">
         <v>3.1</v>
       </c>
-      <c r="T35">
-        <v>2.84</v>
-      </c>
       <c r="U35">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="V35">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="Z35">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AA35">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="AB35">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="AC35">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AD35">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AE35">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>2.64</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AH35">
-        <v>5.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI35">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="s">
         <v>248</v>
@@ -7020,13 +7020,13 @@
         <v>248</v>
       </c>
       <c r="AL35">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AM35">
         <v>0</v>
       </c>
       <c r="AN35">
-        <v>3.7</v>
+        <v>1.28</v>
       </c>
       <c r="AO35">
         <v>-1</v>
@@ -7085,7 +7085,7 @@
         <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
         <v>106</v>
@@ -7112,76 +7112,76 @@
         <v>247</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ36" t="s">
         <v>248</v>
@@ -7190,46 +7190,46 @@
         <v>248</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AM36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO36">
         <v>-1</v>
       </c>
       <c r="AP36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU36">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AV36">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AW36">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AY36">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ36">
         <v>0</v>
@@ -7238,10 +7238,10 @@
         <v>0</v>
       </c>
       <c r="BB36">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BC36">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD36" s="3">
         <v>45837.5</v>
@@ -7282,76 +7282,76 @@
         <v>247</v>
       </c>
       <c r="L37">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="M37">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N37">
-        <v>3.47</v>
+        <v>4</v>
       </c>
       <c r="O37">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="P37">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q37">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="R37">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S37">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="T37">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U37">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V37">
-        <v>6.65</v>
+        <v>7.3</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z37">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AA37">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AB37">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AC37">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AD37">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE37">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH37">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI37">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="s">
         <v>248</v>
@@ -7360,46 +7360,46 @@
         <v>248</v>
       </c>
       <c r="AL37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM37">
         <v>1.22</v>
       </c>
       <c r="AN37">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AO37">
         <v>-1</v>
       </c>
       <c r="AP37">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="AR37">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AS37">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AT37">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AU37">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="AV37">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AW37">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="AX37">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AY37">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AZ37">
         <v>0</v>
@@ -7408,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BC37">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="BD37" s="3">
         <v>45837.5</v>
@@ -7452,124 +7452,124 @@
         <v>247</v>
       </c>
       <c r="L38">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="M38">
-        <v>3.08</v>
+        <v>3.39</v>
       </c>
       <c r="N38">
-        <v>2.85</v>
+        <v>3.47</v>
       </c>
       <c r="O38">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="P38">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q38">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="R38">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="S38">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U38">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V38">
-        <v>9.1</v>
+        <v>6.65</v>
       </c>
       <c r="W38">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z38">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AA38">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="AB38">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AC38">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AD38">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE38">
+        <v>1.35</v>
+      </c>
+      <c r="AF38">
+        <v>1.7</v>
+      </c>
+      <c r="AG38">
+        <v>2</v>
+      </c>
+      <c r="AH38">
+        <v>5.75</v>
+      </c>
+      <c r="AI38">
+        <v>1.12</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL38">
+        <v>1.25</v>
+      </c>
+      <c r="AM38">
         <v>1.22</v>
       </c>
-      <c r="AF38">
+      <c r="AN38">
         <v>1.85</v>
-      </c>
-      <c r="AG38">
-        <v>1.8</v>
-      </c>
-      <c r="AH38">
-        <v>8.5</v>
-      </c>
-      <c r="AI38">
-        <v>1.06</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL38">
-        <v>1.38</v>
-      </c>
-      <c r="AM38">
-        <v>1.3</v>
-      </c>
-      <c r="AN38">
-        <v>1.53</v>
       </c>
       <c r="AO38">
         <v>-1</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AQ38">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AR38">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AS38">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AT38">
-        <v>3.15</v>
+        <v>2.33</v>
       </c>
       <c r="AU38">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="AV38">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="AW38">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AX38">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AY38">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AZ38">
         <v>0</v>
@@ -7578,10 +7578,10 @@
         <v>0</v>
       </c>
       <c r="BB38">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="BC38">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="BD38" s="3">
         <v>45837.5</v>
@@ -7595,7 +7595,7 @@
         <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
         <v>106</v>
@@ -7622,76 +7622,76 @@
         <v>247</v>
       </c>
       <c r="L39">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="s">
         <v>248</v>
@@ -7700,46 +7700,46 @@
         <v>248</v>
       </c>
       <c r="AL39">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO39">
         <v>-1</v>
       </c>
       <c r="AP39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ39">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR39">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS39">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT39">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU39">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV39">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW39">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX39">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY39">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ39">
         <v>0</v>
@@ -7748,10 +7748,10 @@
         <v>0</v>
       </c>
       <c r="BB39">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BC39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BD39" s="3">
         <v>45837.5</v>
@@ -8105,7 +8105,7 @@
         <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D42" t="s">
         <v>106</v>
@@ -8275,7 +8275,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
         <v>106</v>
@@ -9662,76 +9662,76 @@
         <v>247</v>
       </c>
       <c r="L51">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="M51">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="N51">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="O51">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P51">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q51">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="S51">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T51">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U51">
+        <v>1.28</v>
+      </c>
+      <c r="V51">
+        <v>6.8</v>
+      </c>
+      <c r="W51">
+        <v>1.01</v>
+      </c>
+      <c r="X51">
+        <v>1.03</v>
+      </c>
+      <c r="Y51">
+        <v>7</v>
+      </c>
+      <c r="Z51">
+        <v>1.44</v>
+      </c>
+      <c r="AA51">
+        <v>2.63</v>
+      </c>
+      <c r="AB51">
+        <v>2.25</v>
+      </c>
+      <c r="AC51">
+        <v>1.53</v>
+      </c>
+      <c r="AD51">
+        <v>4.25</v>
+      </c>
+      <c r="AE51">
         <v>1.2</v>
       </c>
-      <c r="V51">
-        <v>12</v>
-      </c>
-      <c r="W51">
-        <v>1</v>
-      </c>
-      <c r="X51">
-        <v>1.07</v>
-      </c>
-      <c r="Y51">
-        <v>5.5</v>
-      </c>
-      <c r="Z51">
-        <v>1.46</v>
-      </c>
-      <c r="AA51">
-        <v>2.55</v>
-      </c>
-      <c r="AB51">
-        <v>2.3</v>
-      </c>
-      <c r="AC51">
-        <v>1.5</v>
-      </c>
-      <c r="AD51">
-        <v>5.75</v>
-      </c>
-      <c r="AE51">
-        <v>1.11</v>
-      </c>
       <c r="AF51">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AG51">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AH51">
-        <v>13</v>
+        <v>8.75</v>
       </c>
       <c r="AI51">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ51" t="s">
         <v>248</v>
@@ -9740,46 +9740,46 @@
         <v>248</v>
       </c>
       <c r="AL51">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AM51">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AN51">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AO51">
         <v>-1</v>
       </c>
       <c r="AP51">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AQ51">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AR51">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS51">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="AT51">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AU51">
-        <v>3.58</v>
+        <v>3.95</v>
       </c>
       <c r="AV51">
-        <v>2.6</v>
+        <v>3.28</v>
       </c>
       <c r="AW51">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AX51">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AY51">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AZ51">
         <v>0</v>
@@ -9788,10 +9788,10 @@
         <v>0</v>
       </c>
       <c r="BB51">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BC51">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="BD51" s="3">
         <v>45837.66666666666</v>
@@ -9805,7 +9805,7 @@
         <v>76</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
         <v>106</v>
@@ -9832,76 +9832,76 @@
         <v>247</v>
       </c>
       <c r="L52">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="M52">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="N52">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="O52">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="P52">
         <v>5.5</v>
       </c>
       <c r="Q52">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="R52">
         <v>1.6</v>
       </c>
       <c r="S52">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T52">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U52">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="V52">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W52">
         <v>1</v>
       </c>
       <c r="X52">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y52">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="Z52">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AA52">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AB52">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC52">
         <v>1.5</v>
       </c>
       <c r="AD52">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AG52">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AH52">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ52" t="s">
         <v>248</v>
@@ -9910,47 +9910,47 @@
         <v>248</v>
       </c>
       <c r="AL52">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AM52">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AN52">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AO52">
         <v>-1</v>
       </c>
       <c r="AP52">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AR52">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AS52">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="AT52">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="AU52">
-        <v>2.28</v>
+        <v>3.58</v>
       </c>
       <c r="AV52">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="AW52">
+        <v>2</v>
+      </c>
+      <c r="AX52">
+        <v>1.65</v>
+      </c>
+      <c r="AY52">
         <v>1.41</v>
       </c>
-      <c r="AX52">
-        <v>1.22</v>
-      </c>
-      <c r="AY52">
-        <v>1.15</v>
-      </c>
       <c r="AZ52">
         <v>0</v>
       </c>
@@ -9958,10 +9958,10 @@
         <v>0</v>
       </c>
       <c r="BB52">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="BC52">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="BD52" s="3">
         <v>45837.66666666666</v>
@@ -10145,7 +10145,7 @@
         <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
         <v>106</v>
@@ -10172,76 +10172,76 @@
         <v>247</v>
       </c>
       <c r="L54">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="M54">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="N54">
+        <v>3.78</v>
+      </c>
+      <c r="O54">
+        <v>1.57</v>
+      </c>
+      <c r="P54">
+        <v>5.5</v>
+      </c>
+      <c r="Q54">
+        <v>3.25</v>
+      </c>
+      <c r="R54">
+        <v>1.6</v>
+      </c>
+      <c r="S54">
+        <v>2.25</v>
+      </c>
+      <c r="T54">
+        <v>3.9</v>
+      </c>
+      <c r="U54">
+        <v>1.23</v>
+      </c>
+      <c r="V54">
+        <v>10</v>
+      </c>
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54">
+        <v>1.05</v>
+      </c>
+      <c r="Y54">
+        <v>7</v>
+      </c>
+      <c r="Z54">
+        <v>1.48</v>
+      </c>
+      <c r="AA54">
+        <v>2.37</v>
+      </c>
+      <c r="AB54">
         <v>2.5</v>
       </c>
-      <c r="O54">
-        <v>1.73</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>2.1</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
-      <c r="V54">
-        <v>0</v>
-      </c>
-      <c r="W54">
-        <v>0</v>
-      </c>
-      <c r="X54">
-        <v>0</v>
-      </c>
-      <c r="Y54">
-        <v>0</v>
-      </c>
-      <c r="Z54">
-        <v>0</v>
-      </c>
-      <c r="AA54">
-        <v>0</v>
-      </c>
-      <c r="AB54">
-        <v>1.57</v>
-      </c>
       <c r="AC54">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH54">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ54" t="s">
         <v>248</v>
@@ -10250,46 +10250,46 @@
         <v>248</v>
       </c>
       <c r="AL54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO54">
         <v>-1</v>
       </c>
       <c r="AP54">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AU54">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AV54">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW54">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AX54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AY54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AZ54">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="BB54">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="BC54">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="BD54" s="3">
         <v>45837.66666666666</v>
@@ -10315,7 +10315,7 @@
         <v>76</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D55" t="s">
         <v>106</v>
@@ -10342,76 +10342,76 @@
         <v>247</v>
       </c>
       <c r="L55">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="M55">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="N55">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P55">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R55">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z55">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA55">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC55">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="AD55">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE55">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF55">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH55">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="AI55">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="s">
         <v>248</v>
@@ -10420,46 +10420,46 @@
         <v>248</v>
       </c>
       <c r="AL55">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AM55">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN55">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO55">
         <v>-1</v>
       </c>
       <c r="AP55">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ55">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR55">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS55">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AT55">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AU55">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV55">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AW55">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AX55">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AY55">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ55">
         <v>0</v>
@@ -10468,10 +10468,10 @@
         <v>0</v>
       </c>
       <c r="BB55">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="BC55">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="BD55" s="3">
         <v>45837.66666666666</v>
@@ -10512,76 +10512,76 @@
         <v>247</v>
       </c>
       <c r="L56">
-        <v>2.03</v>
+        <v>1.31</v>
       </c>
       <c r="M56">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="N56">
-        <v>2.83</v>
+        <v>6.8</v>
       </c>
       <c r="O56">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="P56">
+        <v>25</v>
+      </c>
+      <c r="Q56">
+        <v>3.46</v>
+      </c>
+      <c r="R56">
+        <v>1.22</v>
+      </c>
+      <c r="S56">
+        <v>4.15</v>
+      </c>
+      <c r="T56">
+        <v>2</v>
+      </c>
+      <c r="U56">
+        <v>1.72</v>
+      </c>
+      <c r="V56">
+        <v>4.6</v>
+      </c>
+      <c r="W56">
+        <v>1.18</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
         <v>19</v>
       </c>
-      <c r="Q56">
-        <v>2.1</v>
-      </c>
-      <c r="R56">
-        <v>1.14</v>
-      </c>
-      <c r="S56">
-        <v>4.5</v>
-      </c>
-      <c r="T56">
-        <v>1.77</v>
-      </c>
-      <c r="U56">
-        <v>1.89</v>
-      </c>
-      <c r="V56">
-        <v>3.4</v>
-      </c>
-      <c r="W56">
-        <v>1.27</v>
-      </c>
-      <c r="X56">
-        <v>1.01</v>
-      </c>
-      <c r="Y56">
-        <v>29</v>
-      </c>
       <c r="Z56">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AA56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB56">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AC56">
-        <v>3.27</v>
+        <v>2.73</v>
       </c>
       <c r="AD56">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AE56">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF56">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AG56">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH56">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="AI56">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AJ56" t="s">
         <v>248</v>
@@ -10590,46 +10590,46 @@
         <v>248</v>
       </c>
       <c r="AL56">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AM56">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AN56">
-        <v>1.67</v>
+        <v>2.85</v>
       </c>
       <c r="AO56">
         <v>-1</v>
       </c>
       <c r="AP56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ56">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AR56">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AS56">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AT56">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AU56">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AV56">
-        <v>4.9</v>
+        <v>3.94</v>
       </c>
       <c r="AW56">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AX56">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AY56">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AZ56">
         <v>0</v>
@@ -10638,10 +10638,10 @@
         <v>0</v>
       </c>
       <c r="BB56">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="BC56">
-        <v>2.1</v>
+        <v>3.46</v>
       </c>
       <c r="BD56" s="3">
         <v>45837.67708333334</v>
@@ -10682,124 +10682,124 @@
         <v>247</v>
       </c>
       <c r="L57">
-        <v>1.31</v>
+        <v>2.03</v>
       </c>
       <c r="M57">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="N57">
-        <v>6.8</v>
+        <v>2.83</v>
       </c>
       <c r="O57">
+        <v>1.75</v>
+      </c>
+      <c r="P57">
+        <v>19</v>
+      </c>
+      <c r="Q57">
+        <v>2.1</v>
+      </c>
+      <c r="R57">
+        <v>1.14</v>
+      </c>
+      <c r="S57">
+        <v>4.5</v>
+      </c>
+      <c r="T57">
+        <v>1.77</v>
+      </c>
+      <c r="U57">
+        <v>1.89</v>
+      </c>
+      <c r="V57">
+        <v>3.4</v>
+      </c>
+      <c r="W57">
+        <v>1.27</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>29</v>
+      </c>
+      <c r="Z57">
+        <v>1.04</v>
+      </c>
+      <c r="AA57">
+        <v>7</v>
+      </c>
+      <c r="AB57">
         <v>1.29</v>
       </c>
-      <c r="P57">
-        <v>25</v>
-      </c>
-      <c r="Q57">
-        <v>3.46</v>
-      </c>
-      <c r="R57">
-        <v>1.22</v>
-      </c>
-      <c r="S57">
-        <v>4.15</v>
-      </c>
-      <c r="T57">
+      <c r="AC57">
+        <v>3.27</v>
+      </c>
+      <c r="AD57">
+        <v>1.73</v>
+      </c>
+      <c r="AE57">
         <v>2</v>
       </c>
-      <c r="U57">
-        <v>1.72</v>
-      </c>
-      <c r="V57">
-        <v>4.6</v>
-      </c>
-      <c r="W57">
-        <v>1.18</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>19</v>
-      </c>
-      <c r="Z57">
-        <v>1.07</v>
-      </c>
-      <c r="AA57">
-        <v>6</v>
-      </c>
-      <c r="AB57">
-        <v>1.4</v>
-      </c>
-      <c r="AC57">
-        <v>2.73</v>
-      </c>
-      <c r="AD57">
-        <v>2</v>
-      </c>
-      <c r="AE57">
+      <c r="AF57">
+        <v>1.3</v>
+      </c>
+      <c r="AG57">
+        <v>3.25</v>
+      </c>
+      <c r="AH57">
+        <v>2.57</v>
+      </c>
+      <c r="AI57">
+        <v>1.43</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK57" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL57">
+        <v>1.25</v>
+      </c>
+      <c r="AM57">
+        <v>1.23</v>
+      </c>
+      <c r="AN57">
         <v>1.67</v>
-      </c>
-      <c r="AF57">
-        <v>1.63</v>
-      </c>
-      <c r="AG57">
-        <v>2.19</v>
-      </c>
-      <c r="AH57">
-        <v>3.2</v>
-      </c>
-      <c r="AI57">
-        <v>1.28</v>
-      </c>
-      <c r="AJ57" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK57" t="s">
-        <v>248</v>
-      </c>
-      <c r="AL57">
-        <v>1.11</v>
-      </c>
-      <c r="AM57">
-        <v>1.13</v>
-      </c>
-      <c r="AN57">
-        <v>2.85</v>
       </c>
       <c r="AO57">
         <v>-1</v>
       </c>
       <c r="AP57">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ57">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR57">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AS57">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AT57">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AU57">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AV57">
-        <v>3.94</v>
+        <v>4.9</v>
       </c>
       <c r="AW57">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="AX57">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="AY57">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AZ57">
         <v>0</v>
@@ -10808,10 +10808,10 @@
         <v>0</v>
       </c>
       <c r="BB57">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="BC57">
-        <v>3.46</v>
+        <v>2.1</v>
       </c>
       <c r="BD57" s="3">
         <v>45837.67708333334</v>

--- a/jogos_2025-06-29.xlsx
+++ b/jogos_2025-06-29.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mt Druitt Town</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.59</v>
+        <v>1.11</v>
       </c>
       <c r="M2" t="n">
-        <v>3.68</v>
+        <v>8.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.26</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['8', '51']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '60']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45837.08333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Mt Druitt Town</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,49 +927,49 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
         <v>2.25</v>
@@ -978,32 +978,32 @@
         <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>['8', '51']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['13', '81']</t>
-        </is>
-      </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45837.08333333334</v>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="M5" t="n">
-        <v>8.5</v>
+        <v>3.74</v>
       </c>
       <c r="N5" t="n">
-        <v>12</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.45</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['13', '81']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['28', '60']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45837.08333333334</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>3.31</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['15', '60']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['9001']</t>
+          <t>['71', '9006']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45837.29166666666</v>
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.08</v>
+        <v>3.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['15', '60']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['71', '9006']</t>
+          <t>['9001']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45837.29166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.59</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>1.64</v>
       </c>
       <c r="O15" t="n">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['2', '90+4']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['6', '10']</t>
+          <t>['43', '65']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45837.33333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '10']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45837.33333333334</v>
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="M20" t="n">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.59</v>
+        <v>3.71</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.33</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['30', '43', '61']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.25</v>
       </c>
-      <c r="X20" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AH20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['20', '50', '53']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45837.375</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="N21" t="n">
-        <v>3.71</v>
+        <v>2.59</v>
       </c>
       <c r="O21" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.44</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['20', '50', '53']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['30', '43', '61']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45837.375</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>3.18</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2.12</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['40', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['15', '32']</t>
+          <t>['22', '45']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45837.41666666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>6.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.18</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
         <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40', '76']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['22', '45']</t>
+          <t>['15', '32']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.52</v>
+        <v>2.51</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45837.41666666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O28" t="n">
         <v>3.3</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.79</v>
-      </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['72', '45', '77']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['26', '39']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.35</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['37', '45', '59', '60', '65']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45837.45833333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>3.63</v>
       </c>
       <c r="M29" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.08</v>
+        <v>1.91</v>
       </c>
       <c r="O29" t="n">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['22', '86']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['25', '58']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45837.45833333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.63</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
         <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.36</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.45</v>
-      </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['22', '86']</t>
+          <t>['37', '45', '59', '60', '65']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['25', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45837.45833333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['72', '45', '77']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['26', '39']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AI31" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45837.45833333334</v>
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="T32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W32" t="n">
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.25</v>
       </c>
-      <c r="X32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['7', '16', '68']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI32" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45837.47916666666</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.45</v>
+        <v>2.33</v>
       </c>
       <c r="M33" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="N33" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O33" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.5</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '16', '68']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45837.47916666666</v>
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,49 +4797,49 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>3.83</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="N34" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="O34" t="n">
-        <v>3.75</v>
+        <v>4.95</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="R34" t="n">
         <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
         <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X34" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA34" t="n">
         <v>3.8</v>
@@ -4848,32 +4848,32 @@
         <v>1.22</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['74', '89']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45837.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O35" t="n">
-        <v>2.79</v>
+        <v>3.75</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.44</v>
+        <v>2.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="X35" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['35', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45837.5</v>
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="M36" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.83</v>
       </c>
-      <c r="U36" t="n">
+      <c r="AD36" t="n">
         <v>1.85</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X36" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['49', '71']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['37', '9004']</t>
+          <t>['34', '41', '56']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45837.5</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.83</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>4.95</v>
+        <v>2.79</v>
       </c>
       <c r="P37" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.54</v>
+        <v>3.44</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="X37" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['35', '60']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD37" t="n">
+      <c r="AI37" t="n">
         <v>1.72</v>
       </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['74', '89']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45837.5</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,109 +5287,109 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P38" t="n">
         <v>3</v>
       </c>
-      <c r="H38" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>8</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.43</v>
-      </c>
       <c r="Q38" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="U38" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.26</v>
+        <v>3.33</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['6', '51', '53']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['28', '73', '78']</t>
+          <t>['37', '9004']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AH38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45837.5</v>
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>4</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD39" t="n">
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['49', '71']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['34', '41', '56']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AI39" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45837.5</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,22 +5545,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.39</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>3.47</v>
+        <v>4.51</v>
       </c>
       <c r="O40" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y40" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Z40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA40" t="n">
         <v>4</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['40', '49', '87']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45837.5</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>4.51</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>2.44</v>
+        <v>1.52</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="R42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.48</v>
       </c>
-      <c r="S42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC42" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['40', '49', '87']</t>
+          <t>['6', '51', '53']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['28', '73', '78']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45837.5</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,19 +6061,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -6083,87 +6083,87 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '76', '84']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45837.54166666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,19 +6190,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -6212,87 +6212,87 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['50', '76', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45837.54166666666</v>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
         <v>2</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,80 +6474,80 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="M47" t="n">
         <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="P47" t="n">
         <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S47" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="U47" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="V47" t="n">
         <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X47" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['18', '29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '66']</t>
         </is>
       </c>
       <c r="AG47" t="n">
         <v>1.29</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AJ47" t="n">
         <v>2.2</v>
@@ -6577,23 +6577,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>2</v>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
@@ -6603,80 +6603,80 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="M48" t="n">
         <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="O48" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="R48" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S48" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="T48" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="U48" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="V48" t="n">
         <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
+          <t>['18', '29']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['52', '66']</t>
         </is>
       </c>
       <c r="AG48" t="n">
         <v>1.29</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AJ48" t="n">
         <v>2.2</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S51" t="n">
         <v>2.25</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T51" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="U51" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W51" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="X51" t="n">
-        <v>3.56</v>
+        <v>2.3</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.31</v>
+        <v>5.25</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45837.625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,25 +7093,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="O52" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P52" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="R52" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ52" t="n">
         <v>2.25</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>['45+3']</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45837.625</v>
@@ -7222,22 +7222,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M53" t="n">
         <v>2.7</v>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="P53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['40', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q53" t="n">
-        <v>4</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y53" t="n">
+      <c r="AI53" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45837.64583333334</v>
@@ -7351,22 +7351,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.1</v>
+        <v>3.16</v>
       </c>
       <c r="M54" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="O54" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="P54" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S54" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="T54" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U54" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V54" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="W54" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X54" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Y54" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AB54" t="n">
         <v>1.04</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['40', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45837.64583333334</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.16</v>
+        <v>2.55</v>
       </c>
       <c r="M55" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N55" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="O55" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="S55" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="T55" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="U55" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V55" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="W55" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="X55" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AA55" t="n">
-        <v>7.2</v>
+        <v>5.99</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7569,20 +7569,20 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45837.64583333334</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,109 +7609,109 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45837.66666666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="M57" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N57" t="n">
-        <v>2.69</v>
+        <v>4.35</v>
       </c>
       <c r="O57" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="P57" t="n">
         <v>1.97</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="R57" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="S57" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ57" t="n">
         <v>3.25</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>['78', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45837.66666666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,109 +7867,109 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45837.66666666666</v>
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P59" t="n">
         <v>1.77</v>
       </c>
-      <c r="M59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O59" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1.97</v>
-      </c>
       <c r="Q59" t="n">
-        <v>5.25</v>
+        <v>5.55</v>
       </c>
       <c r="R59" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="S59" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="T59" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="U59" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="V59" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="W59" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="X59" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AA59" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45837.66666666666</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X61" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC61" t="n">
         <v>2</v>
       </c>
-      <c r="M61" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="N61" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O61" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P61" t="n">
+      <c r="AD61" t="n">
         <v>1.77</v>
       </c>
-      <c r="Q61" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T61" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X61" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78', '90+4']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45837.66666666666</v>
@@ -8641,25 +8641,25 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M64" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="N64" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O64" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P64" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q64" t="n">
         <v>5</v>
       </c>
       <c r="R64" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="T64" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="U64" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V64" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W64" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="X64" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="Y64" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH64" t="n">
         <v>2</v>
       </c>
-      <c r="Z64" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>['12', '21', '81']</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI64" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45837.6875</v>
@@ -8770,25 +8770,25 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="M65" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="N65" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O65" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P65" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q65" t="n">
         <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S65" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="T65" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>['12', '21', '81']</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
         <v>1.28</v>
       </c>
-      <c r="V65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>['2']</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH65" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AJ65" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45837.6875</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,22 +8899,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>2</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S66" t="n">
         <v>3.6</v>
       </c>
-      <c r="N66" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O66" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P66" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="T66" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>['69', '79']</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>['45+1', '40', '83']</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
         <v>1.25</v>
       </c>
-      <c r="S66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X66" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>['40', '79']</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>['19', '45+1']</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH66" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ66" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45837.70833333334</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,22 +9028,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>2</v>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="M67" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N67" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="O67" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="P67" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="R67" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S67" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T67" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="U67" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W67" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X67" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y67" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>['40', '79']</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>['19', '45+1']</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI67" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z67" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>['69', '79']</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['45+1', '40', '83']</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45837.70833333334</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,25 +9415,25 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -9441,83 +9441,83 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="M70" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="N70" t="n">
-        <v>3.43</v>
+        <v>3.15</v>
       </c>
       <c r="O70" t="n">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="P70" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>5.79</v>
       </c>
       <c r="R70" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="S70" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="T70" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U70" t="n">
         <v>1.27</v>
       </c>
       <c r="V70" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W70" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="X70" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AA70" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['83', '90+2']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['89', '90+7']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AI70" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45837.79166666666</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,25 +9673,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9699,83 +9699,83 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P72" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T72" t="n">
         <v>3.3</v>
       </c>
-      <c r="N72" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O72" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P72" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S72" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U72" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V72" t="n">
         <v>1.04</v>
       </c>
       <c r="W72" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="X72" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD72" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z72" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['4502']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '64']</t>
         </is>
       </c>
       <c r="AG72" t="n">
         <v>1.25</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ72" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45837.79166666666</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
         <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M73" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="O73" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="P73" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="R73" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="S73" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="T73" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U73" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V73" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W73" t="n">
         <v>1.46</v>
       </c>
       <c r="X73" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA73" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>['26', '64']</t>
+          <t>['89', '90+7']</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45837.79166666666</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,109 +9931,109 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O74" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P74" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X74" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH74" t="n">
         <v>2</v>
       </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="M74" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N74" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O74" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P74" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T74" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U74" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V74" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X74" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>['83', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AG74" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AI74" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>45837.79166666666</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,109 +10060,109 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="M75" t="n">
-        <v>4.12</v>
+        <v>3.1</v>
       </c>
       <c r="N75" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="O75" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P75" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.44</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="S75" t="n">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="T75" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="U75" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W75" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="X75" t="n">
-        <v>6.25</v>
+        <v>2.61</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="Z75" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.83</v>
+        <v>5.01</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.86</v>
+        <v>1.17</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AD75" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AI75" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ75" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>45837.83333333334</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,22 +10189,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
@@ -10215,83 +10215,83 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="M76" t="n">
-        <v>3.1</v>
+        <v>3.69</v>
       </c>
       <c r="N76" t="n">
-        <v>3.25</v>
+        <v>1.97</v>
       </c>
       <c r="O76" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="P76" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R76" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="S76" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="T76" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="V76" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W76" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="X76" t="n">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.5</v>
+        <v>2.82</v>
       </c>
       <c r="AA76" t="n">
-        <v>5.01</v>
+        <v>2</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['15', '67']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['73', '89', '9']</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45837.83333333334</v>
@@ -10318,19 +10318,19 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -10340,87 +10340,87 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.52</v>
+        <v>2.85</v>
       </c>
       <c r="M77" t="n">
-        <v>4.3</v>
+        <v>4.12</v>
       </c>
       <c r="N77" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="O77" t="n">
-        <v>2.07</v>
+        <v>3.12</v>
       </c>
       <c r="P77" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="R77" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S77" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T77" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="U77" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X77" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.31</v>
+        <v>1.83</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1', '-1', '-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1', '-1', '-1', '-1', '-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AH77" t="n">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AJ77" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45837.83333333334</v>
@@ -10447,25 +10447,25 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -10473,83 +10473,83 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.01</v>
+        <v>1.52</v>
       </c>
       <c r="M78" t="n">
-        <v>3.69</v>
+        <v>4.3</v>
       </c>
       <c r="N78" t="n">
-        <v>1.97</v>
+        <v>4.7</v>
       </c>
       <c r="O78" t="n">
-        <v>3.32</v>
+        <v>2.07</v>
       </c>
       <c r="P78" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S78" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="U78" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="V78" t="n">
         <v>1.01</v>
       </c>
       <c r="W78" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X78" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.82</v>
+        <v>2.51</v>
       </c>
       <c r="AA78" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>['15', '67']</t>
+          <t>['-1', '-1', '-1', '-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>['73', '89', '9']</t>
+          <t>['-1', '-1', '-1', '-1', '-1', '-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="AI78" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AJ78" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45837.83333333334</v>
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N81" t="n">
-        <v>3.39</v>
+        <v>4.6</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
